--- a/docs/reports/fyuz_graduation_v3.xlsx
+++ b/docs/reports/fyuz_graduation_v3.xlsx
@@ -182,6 +182,9 @@
           </tx>
           <spPr>
             <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -221,7 +224,8 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="7"/>
             <spPr>
               <a:ln>
                 <a:prstDash val="solid"/>
@@ -247,7 +251,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <title>
           <tx>
             <rich>
@@ -284,7 +288,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Price (BNB per token)</a:t>
+                  <a:t>Price (×1e-9 BNB per token)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -336,6 +340,9 @@
           </tx>
           <spPr>
             <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -375,7 +382,8 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="7"/>
             <spPr>
               <a:ln>
                 <a:prstDash val="solid"/>
@@ -401,7 +409,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <title>
           <tx>
             <rich>
@@ -438,7 +446,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Price (USD per token)</a:t>
+                  <a:t>Price (×1e-6 USD per token)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -522,7 +530,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <title>
           <tx>
             <rich>
@@ -1177,12 +1185,12 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Price (BNB/token)</t>
+          <t>Price (×1e-9 BNB/token)</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Price (USD/token)</t>
+          <t>Price (×1e-6 USD/token)</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
@@ -1192,22 +1200,22 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Curve Price (BNB)</t>
+          <t>Curve Price (×1e-9 BNB)</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>DEX Price (BNB)</t>
+          <t>DEX Price (×1e-9 BNB)</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Curve Price (USD)</t>
+          <t>Curve Price (×1e-6 USD)</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>DEX Price (USD)</t>
+          <t>DEX Price (×1e-6 USD)</t>
         </is>
       </c>
     </row>
@@ -1224,19 +1232,19 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>7.688723205e-09</v>
+        <v>7.68872</v>
       </c>
       <c r="E2" t="n">
-        <v>4.358803384821295e-06</v>
+        <v>4.3588</v>
       </c>
       <c r="F2" t="n">
         <v>4358.8</v>
       </c>
       <c r="G2" t="n">
-        <v>7.688723205e-09</v>
+        <v>7.68872</v>
       </c>
       <c r="I2" t="n">
-        <v>4.358803384821295e-06</v>
+        <v>4.3588</v>
       </c>
     </row>
     <row r="3">
@@ -1252,19 +1260,19 @@
         <v>0.4</v>
       </c>
       <c r="D3" t="n">
-        <v>8.444555452000001e-09</v>
+        <v>8.44456</v>
       </c>
       <c r="E3" t="n">
-        <v>4.787291193361241e-06</v>
+        <v>4.78729</v>
       </c>
       <c r="F3" t="n">
         <v>4787.29</v>
       </c>
       <c r="G3" t="n">
-        <v>8.444555452000001e-09</v>
+        <v>8.44456</v>
       </c>
       <c r="I3" t="n">
-        <v>4.787291193361241e-06</v>
+        <v>4.78729</v>
       </c>
     </row>
     <row r="4">
@@ -1280,19 +1288,19 @@
         <v>0.8</v>
       </c>
       <c r="D4" t="n">
-        <v>9.235817334000001e-09</v>
+        <v>9.23582</v>
       </c>
       <c r="E4" t="n">
-        <v>5.235864367031845e-06</v>
+        <v>5.23586</v>
       </c>
       <c r="F4" t="n">
         <v>5235.86</v>
       </c>
       <c r="G4" t="n">
-        <v>9.235817334000001e-09</v>
+        <v>9.23582</v>
       </c>
       <c r="I4" t="n">
-        <v>5.235864367031845e-06</v>
+        <v>5.23586</v>
       </c>
     </row>
     <row r="5">
@@ -1308,19 +1316,19 @@
         <v>1.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0062508853e-08</v>
+        <v>10.0625</v>
       </c>
       <c r="E5" t="n">
-        <v>5.704522906966925e-06</v>
+        <v>5.70452</v>
       </c>
       <c r="F5" t="n">
         <v>5704.52</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0062508853e-08</v>
+        <v>10.0625</v>
       </c>
       <c r="I5" t="n">
-        <v>5.704522906966925e-06</v>
+        <v>5.70452</v>
       </c>
     </row>
     <row r="6">
@@ -1336,19 +1344,19 @@
         <v>1.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0924630009e-08</v>
+        <v>10.9246</v>
       </c>
       <c r="E6" t="n">
-        <v>6.193266813166477e-06</v>
+        <v>6.19327</v>
       </c>
       <c r="F6" t="n">
         <v>6193.27</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0924630009e-08</v>
+        <v>10.9246</v>
       </c>
       <c r="I6" t="n">
-        <v>6.193266813166477e-06</v>
+        <v>6.19327</v>
       </c>
     </row>
     <row r="7">
@@ -1364,19 +1372,19 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1822180801e-08</v>
+        <v>11.8222</v>
       </c>
       <c r="E7" t="n">
-        <v>6.702096085063596e-06</v>
+        <v>6.7021</v>
       </c>
       <c r="F7" t="n">
         <v>6702.1</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1822180801e-08</v>
+        <v>11.8222</v>
       </c>
       <c r="I7" t="n">
-        <v>6.702096085063596e-06</v>
+        <v>6.7021</v>
       </c>
     </row>
     <row r="8">
@@ -1392,19 +1400,19 @@
         <v>2.4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.275516123e-08</v>
+        <v>12.7552</v>
       </c>
       <c r="E8" t="n">
-        <v>7.23101072322519e-06</v>
+        <v>7.23101</v>
       </c>
       <c r="F8" t="n">
         <v>7231.01</v>
       </c>
       <c r="G8" t="n">
-        <v>1.275516123e-08</v>
+        <v>12.7552</v>
       </c>
       <c r="I8" t="n">
-        <v>7.23101072322519e-06</v>
+        <v>7.23101</v>
       </c>
     </row>
     <row r="9">
@@ -1420,19 +1428,19 @@
         <v>2.8</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3723571295e-08</v>
+        <v>13.7236</v>
       </c>
       <c r="E9" t="n">
-        <v>7.780010727084348e-06</v>
+        <v>7.78001</v>
       </c>
       <c r="F9" t="n">
         <v>7780.01</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3723571295e-08</v>
+        <v>13.7236</v>
       </c>
       <c r="I9" t="n">
-        <v>7.780010727084348e-06</v>
+        <v>7.78001</v>
       </c>
     </row>
     <row r="10">
@@ -1448,19 +1456,19 @@
         <v>3.2</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4727410997e-08</v>
+        <v>14.7274</v>
       </c>
       <c r="E10" t="n">
-        <v>8.349096097207983e-06</v>
+        <v>8.3491</v>
       </c>
       <c r="F10" t="n">
         <v>8349.1</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4727410997e-08</v>
+        <v>14.7274</v>
       </c>
       <c r="I10" t="n">
-        <v>8.349096097207983e-06</v>
+        <v>8.3491</v>
       </c>
     </row>
     <row r="11">
@@ -1476,19 +1484,19 @@
         <v>3.6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5766680335e-08</v>
+        <v>15.7667</v>
       </c>
       <c r="E11" t="n">
-        <v>8.938266833029184e-06</v>
+        <v>8.93827</v>
       </c>
       <c r="F11" t="n">
         <v>8938.27</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5766680335e-08</v>
+        <v>15.7667</v>
       </c>
       <c r="I11" t="n">
-        <v>8.938266833029184e-06</v>
+        <v>8.93827</v>
       </c>
     </row>
     <row r="12">
@@ -1504,19 +1512,19 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.684137931e-08</v>
+        <v>16.8414</v>
       </c>
       <c r="E12" t="n">
-        <v>9.547522935114858e-06</v>
+        <v>9.54752</v>
       </c>
       <c r="F12" t="n">
         <v>9547.52</v>
       </c>
       <c r="G12" t="n">
-        <v>1.684137931e-08</v>
+        <v>16.8414</v>
       </c>
       <c r="I12" t="n">
-        <v>9.547522935114858e-06</v>
+        <v>9.54752</v>
       </c>
     </row>
     <row r="13">
@@ -1532,19 +1540,19 @@
         <v>4.4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.7951507921e-08</v>
+        <v>17.9515</v>
       </c>
       <c r="E13" t="n">
-        <v>1.01768644028981e-05</v>
+        <v>10.1769</v>
       </c>
       <c r="F13" t="n">
         <v>10176.86</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7951507921e-08</v>
+        <v>17.9515</v>
       </c>
       <c r="I13" t="n">
-        <v>1.01768644028981e-05</v>
+        <v>10.1769</v>
       </c>
     </row>
     <row r="14">
@@ -1560,19 +1568,19 @@
         <v>4.8</v>
       </c>
       <c r="D14" t="n">
-        <v>1.9097066169e-08</v>
+        <v>19.0971</v>
       </c>
       <c r="E14" t="n">
-        <v>1.082629123694581e-05</v>
+        <v>10.8263</v>
       </c>
       <c r="F14" t="n">
         <v>10826.29</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9097066169e-08</v>
+        <v>19.0971</v>
       </c>
       <c r="I14" t="n">
-        <v>1.082629123694581e-05</v>
+        <v>10.8263</v>
       </c>
     </row>
     <row r="15">
@@ -1588,19 +1596,19 @@
         <v>5.2</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0278054054e-08</v>
+        <v>20.2781</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1495803437258e-05</v>
+        <v>11.4958</v>
       </c>
       <c r="F15" t="n">
         <v>11495.8</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0278054054e-08</v>
+        <v>20.2781</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1495803437258e-05</v>
+        <v>11.4958</v>
       </c>
     </row>
     <row r="16">
@@ -1616,19 +1624,19 @@
         <v>5.6</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1494471575e-08</v>
+        <v>21.4945</v>
       </c>
       <c r="E16" t="n">
-        <v>1.218540100326776e-05</v>
+        <v>12.1854</v>
       </c>
       <c r="F16" t="n">
         <v>12185.4</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1494471575e-08</v>
+        <v>21.4945</v>
       </c>
       <c r="I16" t="n">
-        <v>1.218540100326776e-05</v>
+        <v>12.1854</v>
       </c>
     </row>
     <row r="17">
@@ -1644,19 +1652,19 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2746318732e-08</v>
+        <v>22.7463</v>
       </c>
       <c r="E17" t="n">
-        <v>1.289508393497508e-05</v>
+        <v>12.8951</v>
       </c>
       <c r="F17" t="n">
         <v>12895.08</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2746318732e-08</v>
+        <v>22.7463</v>
       </c>
       <c r="I17" t="n">
-        <v>1.289508393497508e-05</v>
+        <v>12.8951</v>
       </c>
     </row>
     <row r="18">
@@ -1672,19 +1680,19 @@
         <v>6.4</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4033595526e-08</v>
+        <v>24.0336</v>
       </c>
       <c r="E18" t="n">
-        <v>1.362485223294688e-05</v>
+        <v>13.6249</v>
       </c>
       <c r="F18" t="n">
         <v>13624.85</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4033595526e-08</v>
+        <v>24.0336</v>
       </c>
       <c r="I18" t="n">
-        <v>1.362485223294688e-05</v>
+        <v>13.6249</v>
       </c>
     </row>
     <row r="19">
@@ -1700,19 +1708,19 @@
         <v>6.8</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5356301957e-08</v>
+        <v>25.3563</v>
       </c>
       <c r="E19" t="n">
-        <v>1.437470589718315e-05</v>
+        <v>14.3747</v>
       </c>
       <c r="F19" t="n">
         <v>14374.71</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5356301957e-08</v>
+        <v>25.3563</v>
       </c>
       <c r="I19" t="n">
-        <v>1.437470589718315e-05</v>
+        <v>14.3747</v>
       </c>
     </row>
     <row r="20">
@@ -1728,19 +1736,19 @@
         <v>7.2</v>
       </c>
       <c r="D20" t="n">
-        <v>2.6714438024e-08</v>
+        <v>26.7144</v>
       </c>
       <c r="E20" t="n">
-        <v>1.514464492711699e-05</v>
+        <v>15.1446</v>
       </c>
       <c r="F20" t="n">
         <v>15144.64</v>
       </c>
       <c r="G20" t="n">
-        <v>2.6714438024e-08</v>
+        <v>26.7144</v>
       </c>
       <c r="I20" t="n">
-        <v>1.514464492711699e-05</v>
+        <v>15.1446</v>
       </c>
     </row>
     <row r="21">
@@ -1756,19 +1764,19 @@
         <v>7.6</v>
       </c>
       <c r="D21" t="n">
-        <v>2.8108003727e-08</v>
+        <v>28.108</v>
       </c>
       <c r="E21" t="n">
-        <v>1.593466932274839e-05</v>
+        <v>15.9347</v>
       </c>
       <c r="F21" t="n">
         <v>15934.67</v>
       </c>
       <c r="G21" t="n">
-        <v>2.8108003727e-08</v>
+        <v>28.108</v>
       </c>
       <c r="I21" t="n">
-        <v>1.593466932274839e-05</v>
+        <v>15.9347</v>
       </c>
     </row>
     <row r="22">
@@ -1784,19 +1792,19 @@
         <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>2.9536999068e-08</v>
+        <v>29.537</v>
       </c>
       <c r="E22" t="n">
-        <v>1.674477908521117e-05</v>
+        <v>16.7448</v>
       </c>
       <c r="F22" t="n">
         <v>16744.78</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9536999068e-08</v>
+        <v>29.537</v>
       </c>
       <c r="I22" t="n">
-        <v>1.674477908521117e-05</v>
+        <v>16.7448</v>
       </c>
     </row>
     <row r="23">
@@ -1812,19 +1820,19 @@
         <v>8.4</v>
       </c>
       <c r="D23" t="n">
-        <v>3.1001424044e-08</v>
+        <v>31.0014</v>
       </c>
       <c r="E23" t="n">
-        <v>1.757497421280462e-05</v>
+        <v>17.575</v>
       </c>
       <c r="F23" t="n">
         <v>17574.97</v>
       </c>
       <c r="G23" t="n">
-        <v>3.1001424044e-08</v>
+        <v>31.0014</v>
       </c>
       <c r="I23" t="n">
-        <v>1.757497421280462e-05</v>
+        <v>17.575</v>
       </c>
     </row>
     <row r="24">
@@ -1840,19 +1848,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>3.2501278657e-08</v>
+        <v>32.5013</v>
       </c>
       <c r="E24" t="n">
-        <v>1.842525470666253e-05</v>
+        <v>18.4253</v>
       </c>
       <c r="F24" t="n">
         <v>18425.25</v>
       </c>
       <c r="G24" t="n">
-        <v>3.2501278657e-08</v>
+        <v>32.5013</v>
       </c>
       <c r="I24" t="n">
-        <v>1.842525470666253e-05</v>
+        <v>18.4253</v>
       </c>
     </row>
     <row r="25">
@@ -1868,19 +1876,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>3.4036562907e-08</v>
+        <v>34.0366</v>
       </c>
       <c r="E25" t="n">
-        <v>1.929562056678493e-05</v>
+        <v>19.2956</v>
       </c>
       <c r="F25" t="n">
         <v>19295.62</v>
       </c>
       <c r="G25" t="n">
-        <v>3.4036562907e-08</v>
+        <v>34.0366</v>
       </c>
       <c r="I25" t="n">
-        <v>1.929562056678493e-05</v>
+        <v>19.2956</v>
       </c>
     </row>
     <row r="26">
@@ -1896,19 +1904,19 @@
         <v>9.6</v>
       </c>
       <c r="D26" t="n">
-        <v>3.5607276794e-08</v>
+        <v>35.6073</v>
       </c>
       <c r="E26" t="n">
-        <v>2.01860717931718e-05</v>
+        <v>20.1861</v>
       </c>
       <c r="F26" t="n">
         <v>20186.07</v>
       </c>
       <c r="G26" t="n">
-        <v>3.5607276794e-08</v>
+        <v>35.6073</v>
       </c>
       <c r="I26" t="n">
-        <v>2.01860717931718e-05</v>
+        <v>20.1861</v>
       </c>
     </row>
     <row r="27">
@@ -1924,19 +1932,19 @@
         <v>10</v>
       </c>
       <c r="D27" t="n">
-        <v>3.7213420316e-08</v>
+        <v>37.2134</v>
       </c>
       <c r="E27" t="n">
-        <v>2.109660838468932e-05</v>
+        <v>21.0966</v>
       </c>
       <c r="F27" t="n">
         <v>21096.61</v>
       </c>
       <c r="G27" t="n">
-        <v>3.7213420316e-08</v>
+        <v>37.2134</v>
       </c>
       <c r="I27" t="n">
-        <v>2.109660838468932e-05</v>
+        <v>21.0966</v>
       </c>
     </row>
     <row r="28">
@@ -1952,19 +1960,19 @@
         <v>10.4</v>
       </c>
       <c r="D28" t="n">
-        <v>3.8854993476e-08</v>
+        <v>38.855</v>
       </c>
       <c r="E28" t="n">
-        <v>2.202723034303823e-05</v>
+        <v>22.0272</v>
       </c>
       <c r="F28" t="n">
         <v>22027.23</v>
       </c>
       <c r="G28" t="n">
-        <v>3.8854993476e-08</v>
+        <v>38.855</v>
       </c>
       <c r="I28" t="n">
-        <v>2.202723034303823e-05</v>
+        <v>22.0272</v>
       </c>
     </row>
     <row r="29">
@@ -1980,19 +1988,19 @@
         <v>10.8</v>
       </c>
       <c r="D29" t="n">
-        <v>4.0531996272e-08</v>
+        <v>40.532</v>
       </c>
       <c r="E29" t="n">
-        <v>2.29779376670847e-05</v>
+        <v>22.9779</v>
       </c>
       <c r="F29" t="n">
         <v>22977.94</v>
       </c>
       <c r="G29" t="n">
-        <v>4.0531996272e-08</v>
+        <v>40.532</v>
       </c>
       <c r="I29" t="n">
-        <v>2.29779376670847e-05</v>
+        <v>22.9779</v>
       </c>
     </row>
     <row r="30">
@@ -2008,19 +2016,19 @@
         <v>11.2</v>
       </c>
       <c r="D30" t="n">
-        <v>4.2244428704e-08</v>
+        <v>42.2444</v>
       </c>
       <c r="E30" t="n">
-        <v>2.394873035682874e-05</v>
+        <v>23.9487</v>
       </c>
       <c r="F30" t="n">
         <v>23948.73</v>
       </c>
       <c r="G30" t="n">
-        <v>4.2244428704e-08</v>
+        <v>42.2444</v>
       </c>
       <c r="I30" t="n">
-        <v>2.394873035682874e-05</v>
+        <v>23.9487</v>
       </c>
     </row>
     <row r="31">
@@ -2036,19 +2044,19 @@
         <v>11.6</v>
       </c>
       <c r="D31" t="n">
-        <v>4.3992290773e-08</v>
+        <v>43.9923</v>
       </c>
       <c r="E31" t="n">
-        <v>2.493960841283725e-05</v>
+        <v>24.9396</v>
       </c>
       <c r="F31" t="n">
         <v>24939.61</v>
       </c>
       <c r="G31" t="n">
-        <v>4.3992290773e-08</v>
+        <v>43.9923</v>
       </c>
       <c r="I31" t="n">
-        <v>2.493960841283725e-05</v>
+        <v>24.9396</v>
       </c>
     </row>
     <row r="32">
@@ -2064,19 +2072,19 @@
         <v>12</v>
       </c>
       <c r="D32" t="n">
-        <v>4.5775582479e-08</v>
+        <v>45.7756</v>
       </c>
       <c r="E32" t="n">
-        <v>2.595057183511024e-05</v>
+        <v>25.9506</v>
       </c>
       <c r="F32" t="n">
         <v>25950.57</v>
       </c>
       <c r="G32" t="n">
-        <v>4.5775582479e-08</v>
+        <v>45.7756</v>
       </c>
       <c r="I32" t="n">
-        <v>2.595057183511024e-05</v>
+        <v>25.9506</v>
       </c>
     </row>
     <row r="33">
@@ -2092,19 +2100,19 @@
         <v>12.4</v>
       </c>
       <c r="D33" t="n">
-        <v>4.7594303821e-08</v>
+        <v>47.5943</v>
       </c>
       <c r="E33" t="n">
-        <v>2.69816206230808e-05</v>
+        <v>26.9816</v>
       </c>
       <c r="F33" t="n">
         <v>26981.62</v>
       </c>
       <c r="G33" t="n">
-        <v>4.7594303821e-08</v>
+        <v>47.5943</v>
       </c>
       <c r="I33" t="n">
-        <v>2.69816206230808e-05</v>
+        <v>26.9816</v>
       </c>
     </row>
     <row r="34">
@@ -2120,19 +2128,19 @@
         <v>12.8</v>
       </c>
       <c r="D34" t="n">
-        <v>4.9448454799e-08</v>
+        <v>49.4485</v>
       </c>
       <c r="E34" t="n">
-        <v>2.803275477674892e-05</v>
+        <v>28.0328</v>
       </c>
       <c r="F34" t="n">
         <v>28032.75</v>
       </c>
       <c r="G34" t="n">
-        <v>4.9448454799e-08</v>
+        <v>49.4485</v>
       </c>
       <c r="I34" t="n">
-        <v>2.803275477674892e-05</v>
+        <v>28.0328</v>
       </c>
     </row>
     <row r="35">
@@ -2148,25 +2156,25 @@
         <v>13.2</v>
       </c>
       <c r="D35" t="n">
-        <v>5.1338035414e-08</v>
+        <v>51.338</v>
       </c>
       <c r="E35" t="n">
-        <v>2.910397429668151e-05</v>
+        <v>29.104</v>
       </c>
       <c r="F35" t="n">
         <v>29103.97</v>
       </c>
       <c r="G35" t="n">
-        <v>5.1338035414e-08</v>
+        <v>51.338</v>
       </c>
       <c r="H35" t="n">
-        <v>5.1338035414e-08</v>
+        <v>51.338</v>
       </c>
       <c r="I35" t="n">
-        <v>2.910397429668151e-05</v>
+        <v>29.104</v>
       </c>
       <c r="J35" t="n">
-        <v>2.910397429668151e-05</v>
+        <v>29.104</v>
       </c>
     </row>
     <row r="36">
@@ -2182,21 +2190,21 @@
         <v>13.6</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>5.2918582414e-08</v>
+        <v>52.9186</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>2.999999999949118e-05</v>
+        <v>30</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>30000</v>
       </c>
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n">
-        <v>5.2918582414e-08</v>
+        <v>52.9186</v>
       </c>
       <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n">
-        <v>2.999999999949118e-05</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
